--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1809-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1809-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B1110F9-60F6-418E-837A-37EDE46C29E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A66B5A2-0C15-4522-86EF-67C357744065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{482AF719-46AF-4A91-B027-F7A6E8D6EB5E}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{8AB56A6F-DE90-40A6-99C6-7489B3BF0DD1}"/>
   </bookViews>
   <sheets>
     <sheet name="1809-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1526,28 +1526,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3F9FCC-5F5C-47F1-A393-BDF63F7A43A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE6336B2-0B17-4B09-BBC9-E5EE3B2C9B74}">
   <dimension ref="A1:X39"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="8" width="6" customWidth="1"/>
-    <col min="9" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1580,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1617,7 +1616,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1669,7 +1668,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1737,7 +1736,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1809,7 +1808,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1881,7 +1880,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1953,7 +1952,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -2025,7 +2024,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="36">
         <v>2020</v>
       </c>
@@ -2097,7 +2096,7 @@
         <v>1.93</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="38">
         <v>2019</v>
       </c>
@@ -2169,7 +2168,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="36">
         <v>2018</v>
       </c>
@@ -2241,7 +2240,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="38">
         <v>2017</v>
       </c>
@@ -2313,7 +2312,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="36">
         <v>2016</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2015</v>
       </c>
@@ -2457,7 +2456,7 @@
         <v>2.12</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="36">
         <v>2014</v>
       </c>
@@ -2529,7 +2528,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2013</v>
       </c>
@@ -2601,7 +2600,7 @@
         <v>2.61</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="36">
         <v>2012</v>
       </c>
@@ -2673,7 +2672,7 @@
         <v>2.36</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2011</v>
       </c>
@@ -2745,7 +2744,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2010</v>
       </c>
@@ -2817,7 +2816,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2009</v>
       </c>
@@ -2889,7 +2888,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2008</v>
       </c>
@@ -2961,7 +2960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2007</v>
       </c>
@@ -3033,7 +3032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2006</v>
       </c>
@@ -3105,7 +3104,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2005</v>
       </c>
@@ -3177,7 +3176,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2004</v>
       </c>
@@ -3249,7 +3248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2003</v>
       </c>
@@ -3321,7 +3320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2002</v>
       </c>
@@ -3393,7 +3392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2001</v>
       </c>
@@ -3465,7 +3464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2000</v>
       </c>
@@ -3537,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>1999</v>
       </c>
@@ -3609,7 +3608,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>1998</v>
       </c>
@@ -3681,7 +3680,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>1997</v>
       </c>
@@ -3753,7 +3752,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <v>1996</v>
       </c>
@@ -3825,7 +3824,7 @@
         <v>6.64</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="40">
         <v>1995</v>
       </c>
@@ -3897,7 +3896,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="42"/>
       <c r="B35" s="43"/>
       <c r="C35" s="19" t="s">
@@ -3925,7 +3924,7 @@
       <c r="W35" s="49"/>
       <c r="X35" s="45"/>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1994</v>
       </c>
@@ -3997,7 +3996,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>1993</v>
       </c>
@@ -4069,7 +4068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1992</v>
       </c>
@@ -4141,7 +4140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38" t="s">
         <v>55</v>
       </c>
